--- a/annotation/Species_list_2022_10_06.xlsx
+++ b/annotation/Species_list_2022_10_06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B848F0-3B49-4A89-BA33-F6FCBDF8B219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56231F09-99F6-41A6-B503-4A0378D56263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER_prevalence" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="255">
   <si>
     <t>Label</t>
   </si>
@@ -785,6 +785,9 @@
   </si>
   <si>
     <t>Merge_With_(2%)</t>
+  </si>
+  <si>
+    <t>Jellies__Hydromedusae</t>
   </si>
 </sst>
 </file>
@@ -2514,7 +2517,9 @@
         <v>245</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="F102" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="G102" s="2"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -3333,6 +3338,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -5075,6 +5083,12 @@
       <c r="C44">
         <v>5.5E-2</v>
       </c>
+      <c r="E44" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -5358,9 +5372,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
         <v>165</v>
       </c>
@@ -5376,9 +5388,6 @@
       <c r="C69">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="E69" t="s">
-        <v>185</v>
-      </c>
       <c r="F69" t="s">
         <v>185</v>
       </c>
@@ -5393,9 +5402,6 @@
       <c r="C70">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="E70" t="s">
-        <v>211</v>
-      </c>
       <c r="F70" t="s">
         <v>211</v>
       </c>
@@ -5410,9 +5416,6 @@
       <c r="C71">
         <v>1.6E-2</v>
       </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
       <c r="F71" t="s">
         <v>8</v>
       </c>
@@ -5444,9 +5447,6 @@
       <c r="C73">
         <v>1.2E-2</v>
       </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
       <c r="F73" t="s">
         <v>8</v>
       </c>
@@ -5460,9 +5460,6 @@
       </c>
       <c r="C74">
         <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="E74" t="s">
-        <v>189</v>
       </c>
       <c r="F74" t="s">
         <v>189</v>
@@ -5734,6 +5731,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">

--- a/annotation/Species_list_2022_10_06.xlsx
+++ b/annotation/Species_list_2022_10_06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56231F09-99F6-41A6-B503-4A0378D56263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD38F59E-9529-4484-A043-1DF4F99BB2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13770" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER_prevalence" sheetId="1" r:id="rId1"/>
@@ -2444,7 +2444,7 @@
         <v>1.9E-2</v>
       </c>
       <c r="F97" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
